--- a/Xr03-13.xlsx
+++ b/Xr03-13.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gerald\Documents\1.Books\1.11th edition\3.Final Excel Files\Chapter 3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jacob\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_B4518F5B4200CCB08B374ABBA4A796AF2CC13880" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="120" windowWidth="15180" windowHeight="8835" firstSheet="1" activeTab="1"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TempBoxPlot" sheetId="5" state="hidden" r:id="rId1"/>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -91,9 +92,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -131,9 +132,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -168,7 +169,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -203,7 +204,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -376,11 +377,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" ht="13" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
     </row>
   </sheetData>
@@ -391,1014 +392,1014 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A201"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" ht="13" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>46</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>46</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>45</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>50</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>40</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>31</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>41</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>38</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>29</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>42</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>33</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>29</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>42</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>37</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>67</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>46</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <v>27</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>40</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <v>33</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
         <v>27</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <v>28</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>29</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>34</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <v>42</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>30</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>34</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <v>38</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <v>30</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
         <v>33</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
         <v>33</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <v>50</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
         <v>50</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
         <v>42</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
         <v>45</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
         <v>37</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
         <v>26</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
         <v>47</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" s="3">
         <v>31</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" s="3">
         <v>27</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" s="3">
         <v>30</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" s="3">
         <v>26</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
         <v>36</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
         <v>46</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
         <v>33</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
         <v>53</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" s="3">
         <v>29</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" s="3">
         <v>38</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" s="3">
         <v>32</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" s="3">
         <v>30</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" s="3">
         <v>44</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" s="3">
         <v>46</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" s="3">
         <v>41</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" s="3">
         <v>40</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" s="3">
         <v>26</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" s="3">
         <v>29</v>
       </c>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" s="3">
         <v>31</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" s="3">
         <v>40</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" s="3">
         <v>26</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" s="3">
         <v>33</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" s="3">
         <v>28</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" s="3">
         <v>27</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" s="3">
         <v>29</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" s="3">
         <v>43</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" s="3">
         <v>37</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" s="3">
         <v>36</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" s="3">
         <v>30</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" s="3">
         <v>26</v>
       </c>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" s="3">
         <v>29</v>
       </c>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" s="3">
         <v>49</v>
       </c>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92" s="3">
         <v>30</v>
       </c>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93" s="3">
         <v>36</v>
       </c>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94" s="3">
         <v>37</v>
       </c>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95" s="3">
         <v>26</v>
       </c>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" s="3">
         <v>30</v>
       </c>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" s="3">
         <v>27</v>
       </c>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" s="3">
         <v>26</v>
       </c>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" s="3">
         <v>27</v>
       </c>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" s="3">
         <v>32</v>
       </c>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" s="3">
         <v>38</v>
       </c>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" s="3">
         <v>42</v>
       </c>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" s="3">
         <v>33</v>
       </c>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104" s="3">
         <v>24</v>
       </c>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105" s="3">
         <v>51</v>
       </c>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A106" s="3">
         <v>46</v>
       </c>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107" s="3">
         <v>45</v>
       </c>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108" s="3">
         <v>48</v>
       </c>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109" s="3">
         <v>33</v>
       </c>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A110" s="3">
         <v>36</v>
       </c>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A111" s="3">
         <v>36</v>
       </c>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A112" s="3">
         <v>49</v>
       </c>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A113" s="3">
         <v>42</v>
       </c>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A114" s="3">
         <v>39</v>
       </c>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115" s="3">
         <v>34</v>
       </c>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A116" s="3">
         <v>29</v>
       </c>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A117" s="3">
         <v>41</v>
       </c>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A118" s="3">
         <v>39</v>
       </c>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A119" s="3">
         <v>61</v>
       </c>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A120" s="3">
         <v>27</v>
       </c>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A121" s="3">
         <v>41</v>
       </c>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A122" s="3">
         <v>38</v>
       </c>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A123" s="3">
         <v>32</v>
       </c>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A124" s="3">
         <v>35</v>
       </c>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A125" s="3">
         <v>43</v>
       </c>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A126" s="3">
         <v>31</v>
       </c>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A127" s="3">
         <v>32</v>
       </c>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A128" s="3">
         <v>31</v>
       </c>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A129" s="3">
         <v>32</v>
       </c>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A130" s="3">
         <v>54</v>
       </c>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A131" s="3">
         <v>42</v>
       </c>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A132" s="3">
         <v>24</v>
       </c>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A133" s="3">
         <v>34</v>
       </c>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A134" s="3">
         <v>38</v>
       </c>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A135" s="3">
         <v>31</v>
       </c>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A136" s="3">
         <v>31</v>
       </c>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A137" s="3">
         <v>30</v>
       </c>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A138" s="3">
         <v>28</v>
       </c>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A139" s="3">
         <v>44</v>
       </c>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A140" s="3">
         <v>26</v>
       </c>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A141" s="3">
         <v>28</v>
       </c>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A142" s="3">
         <v>37</v>
       </c>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A143" s="3">
         <v>41</v>
       </c>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A144" s="3">
         <v>33</v>
       </c>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A145" s="3">
         <v>57</v>
       </c>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A146" s="3">
         <v>36</v>
       </c>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A147" s="3">
         <v>33</v>
       </c>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A148" s="3">
         <v>29</v>
       </c>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A149" s="3">
         <v>43</v>
       </c>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A150" s="3">
         <v>32</v>
       </c>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A151" s="3">
         <v>33</v>
       </c>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A152" s="3">
         <v>45</v>
       </c>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A153" s="3">
         <v>32</v>
       </c>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A154" s="3">
         <v>33</v>
       </c>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A155" s="3">
         <v>28</v>
       </c>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A156" s="3">
         <v>35</v>
       </c>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A157" s="3">
         <v>28</v>
       </c>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A158" s="3">
         <v>38</v>
       </c>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A159" s="3">
         <v>29</v>
       </c>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A160" s="3">
         <v>29</v>
       </c>
     </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A161" s="3">
         <v>24</v>
       </c>
     </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A162" s="3">
         <v>38</v>
       </c>
     </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A163" s="3">
         <v>51</v>
       </c>
     </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A164" s="3">
         <v>35</v>
       </c>
     </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A165" s="3">
         <v>37</v>
       </c>
     </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A166" s="3">
         <v>29</v>
       </c>
     </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A167" s="3">
         <v>29</v>
       </c>
     </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A168" s="3">
         <v>33</v>
       </c>
     </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A169" s="3">
         <v>28</v>
       </c>
     </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A170" s="3">
         <v>45</v>
       </c>
     </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A171" s="3">
         <v>24</v>
       </c>
     </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A172" s="3">
         <v>25</v>
       </c>
     </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A173" s="3">
         <v>29</v>
       </c>
     </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A174" s="3">
         <v>36</v>
       </c>
     </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A175" s="3">
         <v>31</v>
       </c>
     </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A176" s="3">
         <v>50</v>
       </c>
     </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A177" s="3">
         <v>32</v>
       </c>
     </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A178" s="3">
         <v>43</v>
       </c>
     </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A179" s="3">
         <v>33</v>
       </c>
     </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A180" s="3">
         <v>36</v>
       </c>
     </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A181" s="3">
         <v>36</v>
       </c>
     </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A182" s="3">
         <v>30</v>
       </c>
     </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A183" s="3">
         <v>28</v>
       </c>
     </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A184" s="3">
         <v>37</v>
       </c>
     </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A185" s="3">
         <v>44</v>
       </c>
     </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A186" s="3">
         <v>35</v>
       </c>
     </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A187" s="3">
         <v>45</v>
       </c>
     </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A188" s="3">
         <v>38</v>
       </c>
     </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A189" s="3">
         <v>29</v>
       </c>
     </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A190" s="3">
         <v>33</v>
       </c>
     </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A191" s="3">
         <v>40</v>
       </c>
     </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A192" s="3">
         <v>54</v>
       </c>
     </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A193" s="3">
         <v>30</v>
       </c>
     </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A194" s="3">
         <v>31</v>
       </c>
     </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A195" s="3">
         <v>26</v>
       </c>
     </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A196" s="3">
         <v>41</v>
       </c>
     </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A197" s="3">
         <v>38</v>
       </c>
     </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A198" s="3">
         <v>36</v>
       </c>
     </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A199" s="3">
         <v>30</v>
       </c>
     </row>
-    <row r="200" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A200" s="3">
         <v>29</v>
       </c>
     </row>
-    <row r="201" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A201" s="3">
         <v>33</v>
       </c>
